--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
@@ -515,15 +515,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Hoja2">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="13.7265625" customWidth="1" min="1" max="1"/>
-    <col width="20.36328125" customWidth="1" min="2" max="2"/>
+    <col width="44.36328125" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
@@ -542,10 +541,8 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
+      <c r="D1" s="4" t="n">
+        <v>2023</v>
       </c>
       <c r="E1" s="4" t="n">
         <v>2024</v>
@@ -597,65 +594,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="N2" s="8" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="O2" s="8" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
+      <c r="D2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -675,40 +648,40 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4002</v>
+        <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>4003</v>
+        <v>0</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>4004</v>
+        <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>4006</v>
+        <v>0</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>4007</v>
+        <v>0</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>4008</v>
+        <v>0</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>4009</v>
+        <v>0</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>4010</v>
+        <v>0</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>4011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -804,65 +777,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -881,65 +830,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -958,65 +883,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -1035,8 +936,10 @@
           <t>years</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>20</v>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -1110,65 +1013,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="15.5" customHeight="1">
@@ -1188,40 +1067,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2001</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2002</v>
+        <v>0</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2003</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2004</v>
+        <v>0</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>2005</v>
+        <v>0</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>2006</v>
+        <v>0</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2007</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>2008</v>
+        <v>0</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>2009</v>
+        <v>0</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>2010</v>
+        <v>0</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>2011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="15.5" customHeight="1">
@@ -1317,65 +1196,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1394,65 +1249,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -1471,65 +1302,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1548,8 +1355,10 @@
           <t>years</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>22</v>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
@@ -1608,13 +1417,13 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Hoja1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1635,10 +1444,8 @@
           <t>Units</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
+      <c r="C1" s="4" t="n">
+        <v>2023</v>
       </c>
       <c r="D1" s="4" t="n">
         <v>2024</v>
@@ -1685,65 +1492,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="N2" s="8" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
+      <c r="C2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -1758,40 +1541,40 @@
         </is>
       </c>
       <c r="C3" s="8" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>4001</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>4002</v>
+        <v>0</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>4003</v>
+        <v>0</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>4004</v>
+        <v>0</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>4006</v>
+        <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>4007</v>
+        <v>0</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>4008</v>
+        <v>0</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>4009</v>
+        <v>0</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>4010</v>
+        <v>0</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>4011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -1877,65 +1660,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="C5" s="8" t="n">
+        <v>0.09441198237754599</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0.1791091825492832</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.1773180907237903</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0.1755449098165524</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0.1737894607183869</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0.1720515661112031</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0.1300782577475552</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0.08872645212259944</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0.08783918760137345</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0.0869607957253597</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0.08609118776810612</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0.07967632839653764</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -1949,65 +1708,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="C6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -2021,65 +1756,41 @@
           <t>M$</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
+      <c r="C7" s="8" t="n">
+        <v>4.32143283622375</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>6.236309089950275</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>8.821590307560108</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>11.35454226990875</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>13.83595303397966</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>16.26660012854216</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>18.64725068591002</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>19.39869399949082</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>19.74037768502499</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>20.07328782744852</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>20.39756572925508</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>20.71335074424277</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -2153,6 +1864,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
@@ -936,65 +936,41 @@
           <t>years</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -1355,65 +1331,41 @@
           <t>years</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1807,60 +1759,38 @@
       <c r="C8" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -595,40 +595,40 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -648,40 +648,40 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0</v>
+        <v>0.09441198237754599</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>0.1791091825492832</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0</v>
+        <v>0.1773180907237903</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0</v>
+        <v>0.1755449098165524</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>0.1737894607183869</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0</v>
+        <v>0.1720515661112031</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0</v>
+        <v>0.1300782577475552</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0</v>
+        <v>0.08872645212259944</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0</v>
+        <v>0.08783918760137345</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0</v>
+        <v>0.0869607957253597</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0</v>
+        <v>0.08609118776810612</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0</v>
+        <v>0.07967632839653764</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -884,40 +884,40 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>0</v>
+        <v>4.32143283622375</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0</v>
+        <v>6.236309089950275</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>0</v>
+        <v>8.821590307560108</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0</v>
+        <v>11.35454226990875</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0</v>
+        <v>13.83595303397966</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0</v>
+        <v>16.26660012854216</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>0</v>
+        <v>18.64725068591002</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>0</v>
+        <v>19.39869399949082</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>0</v>
+        <v>19.74037768502499</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>0</v>
+        <v>20.07328782744852</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>0</v>
+        <v>20.39756572925508</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>0</v>
+        <v>20.71335074424277</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
@@ -990,40 +990,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" ht="15.5" customHeight="1">
@@ -1043,40 +1043,40 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="15.5" customHeight="1">
@@ -1173,40 +1173,40 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1279,40 +1279,40 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0</v>
@@ -1375,17 +1375,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Hoja1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.81640625" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1">
+    <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Inputs</t>
@@ -1433,7 +1433,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="2" ht="15.5" customHeight="1">
+    <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Tariff</t>
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15.5" customHeight="1">
+    <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Demand</t>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="15.5" customHeight="1">
+    <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Outputs</t>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.5" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CAPEX - Growth</t>
@@ -1649,7 +1649,7 @@
         <v>0.07967632839653764</v>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>CAPEX - Maintenance</t>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="15.5" customHeight="1">
+    <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -1745,7 +1745,7 @@
         <v>20.71335074424277</v>
       </c>
     </row>
-    <row r="8" ht="15.5" customHeight="1">
+    <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>D&amp;A</t>
@@ -1794,6 +1794,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="C2" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1613,40 +1613,40 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.09441198237754599</v>
+        <v>0.09</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.1791091825492832</v>
+        <v>0.18</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.1773180907237903</v>
+        <v>0.18</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.1755449098165524</v>
+        <v>0.18</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.1737894607183869</v>
+        <v>0.17</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.1720515661112031</v>
+        <v>0.17</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.1300782577475552</v>
+        <v>0.13</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.08872645212259944</v>
+        <v>0.09</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.08783918760137345</v>
+        <v>0.09</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.0869607957253597</v>
+        <v>0.09</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.08609118776810612</v>
+        <v>0.09</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0.07967632839653764</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="6">
@@ -1709,40 +1709,40 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>4.32143283622375</v>
+        <v>4.32</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>6.236309089950275</v>
+        <v>6.24</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>8.821590307560108</v>
+        <v>8.82</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>11.35454226990875</v>
+        <v>11.35</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>13.83595303397966</v>
+        <v>13.84</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>16.26660012854216</v>
+        <v>16.27</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>18.64725068591002</v>
+        <v>18.65</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>19.39869399949082</v>
+        <v>19.4</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>19.74037768502499</v>
+        <v>19.74</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>20.07328782744852</v>
+        <v>20.07</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>20.39756572925508</v>
+        <v>20.4</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>20.71335074424277</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="8">
@@ -1759,38 +1759,60 @@
       <c r="C8" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>0</v>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ethanol" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
@@ -1818,4 +1819,451 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20.81640625" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D1" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F1" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G1" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="H1" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="I1" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J1" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="K1" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="L1" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="M1" s="4" t="n">
+        <v>2033</v>
+      </c>
+      <c r="N1" s="4" t="n">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Tariff</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>$/kWh</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Maintenance</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -8,7 +8,6 @@
   <sheets>
     <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ethanol" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
@@ -17,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -135,7 +137,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -175,6 +177,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -520,10 +538,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col width="44.36328125" customWidth="1" min="1" max="1"/>
+    <col width="15.1796875" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="9.08984375" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.5" customHeight="1">
@@ -596,40 +616,40 @@
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>8</v>
+        <v>0.15</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>8</v>
+        <v>0.1575</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>8</v>
+        <v>0.165375</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>8</v>
+        <v>0.17364375</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>8</v>
+        <v>0.1823259375000001</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>8</v>
+        <v>0.1914422343750001</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>8</v>
+        <v>0.2010143460937501</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>8</v>
+        <v>0.2110650633984376</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>8</v>
+        <v>0.2216183165683595</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>8</v>
+        <v>0.2326992323967775</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>8</v>
+        <v>0.2443341940166164</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>8</v>
+        <v>0.2565509037174472</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -649,40 +669,40 @@
         </is>
       </c>
       <c r="D3" s="8" t="n">
-        <v>9</v>
+        <v>1473.5735</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>9</v>
+        <v>1616.8539</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>9</v>
+        <v>1793.1866</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>9</v>
+        <v>1954.5022</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>9</v>
+        <v>2101.5716</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>9</v>
+        <v>2235.1395</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>9</v>
+        <v>2355.9236</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>9</v>
+        <v>2518.5404</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>9</v>
+        <v>2659.5132</v>
       </c>
       <c r="M3" s="8" t="n">
-        <v>9</v>
+        <v>2786.3986</v>
       </c>
       <c r="N3" s="8" t="n">
-        <v>9</v>
+        <v>3222.2</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>9</v>
+        <v>3001.0062</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -779,40 +799,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.09441198237754599</v>
+        <v>257.2547513691348</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.1791091825492832</v>
+        <v>324.6150491019822</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.1773180907237903</v>
+        <v>321.3688986109623</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.1755449098165524</v>
+        <v>318.1552096248527</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.1737894607183869</v>
+        <v>314.9736575286042</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.1720515661112031</v>
+        <v>311.8239209533182</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.1300782577475552</v>
+        <v>382.0048802582858</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.08872645212259944</v>
+        <v>451.1166131276156</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.08783918760137345</v>
+        <v>446.6054469963394</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.0869607957253597</v>
+        <v>442.139392526376</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0.08609118776810612</v>
+        <v>437.7179986011122</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>0.07967632839653764</v>
+        <v>290.7814303112916</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -885,40 +905,40 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>4.32143283622375</v>
+        <v>48.20089562467992</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>6.236309089950275</v>
+        <v>54.57954899290949</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>8.821590307560108</v>
+        <v>62.19293437018627</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>11.35454226990875</v>
+        <v>69.64859408501823</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>13.83595303397966</v>
+        <v>76.94892131211654</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>16.26660012854216</v>
+        <v>84.09627713526439</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>18.64725068591002</v>
+        <v>91.09299094981805</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>19.39869399949082</v>
+        <v>102.1514263745141</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>19.74037768502499</v>
+        <v>112.6977094229257</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>20.07328782744852</v>
+        <v>123.0228516677316</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>20.39756572925508</v>
+        <v>133.1302212966991</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>20.71335074424277</v>
+        <v>143.0231412479205</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -938,7 +958,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0</v>
@@ -991,40 +1011,40 @@
         </is>
       </c>
       <c r="D9" s="8" t="n">
-        <v>10</v>
+        <v>0.15</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>10</v>
+        <v>0.1575</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>10</v>
+        <v>0.165375</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>10</v>
+        <v>0.17364375</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>10</v>
+        <v>0.1823259375000001</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>10</v>
+        <v>0.1914422343750001</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>10</v>
+        <v>0.2010143460937501</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>10</v>
+        <v>0.2110650633984376</v>
       </c>
       <c r="L9" s="8" t="n">
-        <v>10</v>
+        <v>0.2216183165683595</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>10</v>
+        <v>0.2326992323967775</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>10</v>
+        <v>0.2443341940166164</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>10</v>
+        <v>0.2565509037174472</v>
       </c>
     </row>
     <row r="10" ht="15.5" customHeight="1">
@@ -1043,41 +1063,43 @@
           <t>kWh</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>11</v>
+      <c r="D10" s="10" t="n">
+        <v>368.3935</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>379.2621</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>393.6264</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>400.3198</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>400.2994</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>394.4365</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>383.5224</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>376.3336</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>362.6608</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>344.3864</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>322.22</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="n">
+        <v>296.8028</v>
       </c>
     </row>
     <row r="11" ht="15.5" customHeight="1">
@@ -1174,40 +1196,40 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>650</v>
+        <v>39.54004604566455</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>650</v>
+        <v>50.33243931157392</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>650</v>
+        <v>49.82911491845817</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>650</v>
+        <v>49.3308237692736</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>650</v>
+        <v>48.83751553158086</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>650</v>
+        <v>48.34914037626506</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>650</v>
+        <v>15.38261584720839</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>650</v>
+        <v>-17.09142019004943</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>650</v>
+        <v>-16.92050598814893</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>650</v>
+        <v>-16.75130092826744</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>650</v>
+        <v>-16.58378791898477</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>650</v>
+        <v>-1.667201492973772</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1280,40 +1302,40 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>56.13416700255231</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>3</v>
+        <v>64.73926242752357</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>3</v>
+        <v>74.87567895765055</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>3</v>
+        <v>84.80289323093224</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>3</v>
+        <v>94.52407565085252</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>3</v>
+        <v>104.0423541330513</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>3</v>
+        <v>113.360814638041</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>3</v>
+        <v>111.5849676293287</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>3</v>
+        <v>105.1265326494934</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>3</v>
+        <v>98.78610787249185</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>3</v>
+        <v>92.56197893776543</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>3</v>
+        <v>86.45245397094627</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1333,7 +1355,7 @@
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0</v>
@@ -1368,9 +1390,13 @@
       <c r="O15" s="10" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="18" ht="15.5" customHeight="1">
+      <c r="D18" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1445,41 +1471,41 @@
           <t>$/kWh</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>2</v>
+      <c r="C2" s="16" t="n">
+        <v>0.076103500761035</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>0.07990867579908675</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>0.0839041095890411</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>0.08809931506849315</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>0.09250428082191782</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.09712949486301371</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>0.1019859696061644</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>0.1070852680864726</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>0.1124395314907963</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>0.1180615080653361</v>
+      </c>
+      <c r="M2" s="14" t="n">
+        <v>0.1239645834686029</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>0.1301628126420331</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -1493,41 +1519,41 @@
           <t>kWh</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>0</v>
+      <c r="C3" s="15" t="n">
+        <v>301.937024</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>326.61092</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>438.647661</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>539.273622</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>629.321493</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>709.570533</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>780.749774</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>970.466594</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>949.431507</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>928.199157</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>906.8360300000001</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>885.402727</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -1614,40 +1640,40 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.09</v>
+        <v>2.682342523664534</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>0.18</v>
+        <v>4.781255564438686</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.18</v>
+        <v>4.760211259164442</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>0.18</v>
+        <v>4.739377396942941</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.17</v>
+        <v>4.718751873343655</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0.17</v>
+        <v>4.698332604980362</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>0.13</v>
+        <v>3.654559875003377</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.09</v>
+        <v>2.617953880133723</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>0.09</v>
+        <v>2.607349780229534</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>0.09</v>
+        <v>2.596851721324386</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>0.09</v>
+        <v>2.586458643008291</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>0.08</v>
+        <v>2.527899077620143</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -1710,40 +1736,40 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>4.32</v>
+        <v>25.44686120688618</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>6.24</v>
+        <v>36.36577111173804</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>8.82</v>
+        <v>51.37173908907033</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>11.35</v>
+        <v>66.31775510398687</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>13.84</v>
+        <v>81.20472209168821</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>16.27</v>
+        <v>96.03353092386709</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>18.65</v>
+        <v>110.8050605596852</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>19.4</v>
+        <v>115.4446554697099</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>19.74</v>
+        <v>118.0951584733858</v>
       </c>
       <c r="L7" s="8" t="n">
-        <v>20.07</v>
+        <v>120.7376308653372</v>
       </c>
       <c r="M7" s="8" t="n">
-        <v>20.4</v>
+        <v>123.3722042626448</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>20.71</v>
+        <v>125.9990084531091</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -1759,453 +1785,6 @@
       </c>
       <c r="C8" s="10" t="n">
         <v>15</v>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20.81640625" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Inputs</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D1" s="4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E1" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F1" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G1" s="4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="H1" s="4" t="n">
-        <v>2028</v>
-      </c>
-      <c r="I1" s="4" t="n">
-        <v>2029</v>
-      </c>
-      <c r="J1" s="4" t="n">
-        <v>2030</v>
-      </c>
-      <c r="K1" s="4" t="n">
-        <v>2031</v>
-      </c>
-      <c r="L1" s="4" t="n">
-        <v>2032</v>
-      </c>
-      <c r="M1" s="4" t="n">
-        <v>2033</v>
-      </c>
-      <c r="N1" s="4" t="n">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>Tariff</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>$/kWh</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Growth</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>8</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>

--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -137,7 +136,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -183,10 +182,6 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -538,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="15.1796875" customWidth="1" min="1" max="1"/>
@@ -607,179 +602,179 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>Tariff</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>$/kWh</t>
+          <t>kWh</t>
         </is>
       </c>
       <c r="D2" s="8" t="n">
-        <v>0.15</v>
+        <v>1473.5735</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>0.1575</v>
+        <v>1616.8539</v>
       </c>
       <c r="F2" s="8" t="n">
-        <v>0.165375</v>
+        <v>1793.1866</v>
       </c>
       <c r="G2" s="8" t="n">
-        <v>0.17364375</v>
+        <v>1954.5022</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>0.1823259375000001</v>
+        <v>2101.5716</v>
       </c>
       <c r="I2" s="8" t="n">
-        <v>0.1914422343750001</v>
+        <v>2235.1395</v>
       </c>
       <c r="J2" s="8" t="n">
-        <v>0.2010143460937501</v>
+        <v>2355.9236</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>0.2110650633984376</v>
+        <v>2518.5404</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>0.2216183165683595</v>
+        <v>2659.5132</v>
       </c>
       <c r="M2" s="8" t="n">
-        <v>0.2326992323967775</v>
+        <v>2786.3986</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>0.2443341940166164</v>
+        <v>3222.2</v>
       </c>
       <c r="O2" s="8" t="n">
-        <v>0.2565509037174472</v>
+        <v>3001.0062</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>GRID</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Outputs</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>1473.5735</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>1616.8539</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>1793.1866</v>
-      </c>
-      <c r="G3" s="8" t="n">
-        <v>1954.5022</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>2101.5716</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>2235.1395</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>2355.9236</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>2518.5404</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>2659.5132</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>2786.3986</v>
-      </c>
-      <c r="N3" s="8" t="n">
-        <v>3222.2</v>
-      </c>
-      <c r="O3" s="8" t="n">
-        <v>3001.0062</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Outputs</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>257.2547513691348</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>324.6150491019822</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>321.3688986109623</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>318.1552096248527</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>314.9736575286042</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>311.8239209533182</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>382.0048802582858</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>451.1166131276156</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>446.6054469963394</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>442.139392526376</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>437.7179986011122</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>290.7814303112916</v>
       </c>
     </row>
     <row r="5" ht="15.5" customHeight="1">
@@ -790,7 +785,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CAPEX - Growth</t>
+          <t>CAPEX - Maintenance</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -799,40 +794,40 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>257.2547513691348</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>324.6150491019822</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>321.3688986109623</v>
+        <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>318.1552096248527</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>314.9736575286042</v>
+        <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>311.8239209533182</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>382.0048802582858</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>451.1166131276156</v>
+        <v>0</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>446.6054469963394</v>
+        <v>0</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>442.139392526376</v>
+        <v>0</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>437.7179986011122</v>
+        <v>0</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>290.7814303112916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -841,9 +836,9 @@
           <t>GRID</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -852,40 +847,40 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>48.20089562467992</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>54.57954899290949</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>62.19293437018627</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>69.64859408501823</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>76.94892131211654</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>84.09627713526439</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0</v>
+        <v>91.09299094981805</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0</v>
+        <v>102.1514263745141</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0</v>
+        <v>112.6977094229257</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0</v>
+        <v>123.0228516677316</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0</v>
+        <v>133.1302212966991</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>0</v>
+        <v>143.0231412479205</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -894,289 +889,289 @@
           <t>GRID</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>OPEX</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.5" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>368.3935</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>379.2621</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>393.6264</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>400.3198</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>400.2994</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>394.4365</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>383.5224</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>376.3336</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>362.6608</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>344.3864</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>322.22</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>296.8028</v>
+      </c>
+    </row>
+    <row r="9" ht="15.5" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
           <t>M$</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>48.20089562467992</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>54.57954899290949</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>62.19293437018627</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>69.64859408501823</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>76.94892131211654</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>84.09627713526439</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>91.09299094981805</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>102.1514263745141</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>112.6977094229257</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>123.0228516677316</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>133.1302212966991</v>
-      </c>
-      <c r="O7" s="8" t="n">
-        <v>143.0231412479205</v>
-      </c>
-    </row>
-    <row r="8" ht="15.5" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15.5" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="D10" s="8" t="n">
+        <v>39.54004604566455</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>50.33243931157392</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>49.82911491845817</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>49.3308237692736</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>48.83751553158086</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>48.34914037626506</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>15.38261584720839</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>-17.09142019004943</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>-16.92050598814893</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>-16.75130092826744</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>-16.58378791898477</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>-1.667201492973772</v>
+      </c>
+    </row>
+    <row r="11" ht="15.5" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Tariff</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>$/kWh</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0.1575</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>0.165375</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>0.17364375</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>0.1823259375000001</v>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>0.1914422343750001</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>0.2010143460937501</v>
-      </c>
-      <c r="K9" s="8" t="n">
-        <v>0.2110650633984376</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>0.2216183165683595</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>0.2326992323967775</v>
-      </c>
-      <c r="N9" s="8" t="n">
-        <v>0.2443341940166164</v>
-      </c>
-      <c r="O9" s="8" t="n">
-        <v>0.2565509037174472</v>
-      </c>
-    </row>
-    <row r="10" ht="15.5" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>368.3935</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>379.2621</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>393.6264</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>400.3198</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>400.2994</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>394.4365</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>383.5224</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>376.3336</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>362.6608</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>344.3864</v>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>322.22</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>296.8028</v>
-      </c>
-    </row>
-    <row r="11" ht="15.5" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Outputs</t>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Maintenance</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O11" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="15.5" customHeight="1">
@@ -1185,9 +1180,9 @@
           <t>OFF-GRID</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Growth</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1196,40 +1191,40 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>39.54004604566455</v>
+        <v>56.13416700255231</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>50.33243931157392</v>
+        <v>64.73926242752357</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>49.82911491845817</v>
+        <v>74.87567895765055</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>49.3308237692736</v>
+        <v>84.80289323093224</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>48.83751553158086</v>
+        <v>94.52407565085252</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>48.34914037626506</v>
+        <v>104.0423541330513</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>15.38261584720839</v>
+        <v>113.360814638041</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>-17.09142019004943</v>
+        <v>111.5849676293287</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>-16.92050598814893</v>
+        <v>105.1265326494934</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>-16.75130092826744</v>
+        <v>98.78610787249185</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>-16.58378791898477</v>
+        <v>92.56197893776543</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>-1.667201492973772</v>
+        <v>86.45245397094627</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1238,161 +1233,55 @@
           <t>OFF-GRID</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15.5" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>56.13416700255231</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>64.73926242752357</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>74.87567895765055</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>84.80289323093224</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>94.52407565085252</v>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>104.0423541330513</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>113.360814638041</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>111.5849676293287</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>105.1265326494934</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>98.78610787249185</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>92.56197893776543</v>
-      </c>
-      <c r="O14" s="8" t="n">
-        <v>86.45245397094627</v>
-      </c>
-    </row>
-    <row r="15" ht="15.5" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
           <t>years</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D13" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15.5" customHeight="1">
-      <c r="D18" s="17" t="n"/>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15.5" customHeight="1">
+      <c r="D16" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1406,7 +1295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="20.81640625" customWidth="1" min="1" max="1"/>
@@ -1463,175 +1352,175 @@
     <row r="2" ht="15.5" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Tariff</t>
+          <t>Demand</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>$/kWh</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="n">
-        <v>0.076103500761035</v>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>301.937024</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>0.07990867579908675</v>
+        <v>326.61092</v>
       </c>
       <c r="E2" s="14" t="n">
-        <v>0.0839041095890411</v>
+        <v>438.647661</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>0.08809931506849315</v>
+        <v>539.273622</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>0.09250428082191782</v>
+        <v>629.321493</v>
       </c>
       <c r="H2" s="14" t="n">
-        <v>0.09712949486301371</v>
+        <v>709.570533</v>
       </c>
       <c r="I2" s="14" t="n">
-        <v>0.1019859696061644</v>
+        <v>780.749774</v>
       </c>
       <c r="J2" s="14" t="n">
-        <v>0.1070852680864726</v>
+        <v>970.466594</v>
       </c>
       <c r="K2" s="14" t="n">
-        <v>0.1124395314907963</v>
+        <v>949.431507</v>
       </c>
       <c r="L2" s="14" t="n">
-        <v>0.1180615080653361</v>
+        <v>928.199157</v>
       </c>
       <c r="M2" s="14" t="n">
-        <v>0.1239645834686029</v>
+        <v>906.8360300000001</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>0.1301628126420331</v>
+        <v>885.402727</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Outputs</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>301.937024</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>326.61092</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>438.647661</v>
-      </c>
-      <c r="F3" s="14" t="n">
-        <v>539.273622</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>629.321493</v>
-      </c>
-      <c r="H3" s="14" t="n">
-        <v>709.570533</v>
-      </c>
-      <c r="I3" s="14" t="n">
-        <v>780.749774</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>970.466594</v>
-      </c>
-      <c r="K3" s="14" t="n">
-        <v>949.431507</v>
-      </c>
-      <c r="L3" s="14" t="n">
-        <v>928.199157</v>
-      </c>
-      <c r="M3" s="14" t="n">
-        <v>906.8360300000001</v>
-      </c>
-      <c r="N3" s="14" t="n">
-        <v>885.402727</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Outputs</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>2.682342523664534</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>4.781255564438686</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>4.760211259164442</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>4.739377396942941</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>4.718751873343655</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>4.698332604980362</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>3.654559875003377</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>2.617953880133723</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>2.607349780229534</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>2.596851721324386</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>2.586458643008291</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>2.527899077620143</v>
       </c>
     </row>
     <row r="5" ht="15.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CAPEX - Growth</t>
+          <t>CAPEX - Maintenance</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1640,46 +1529,46 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2.682342523664534</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>4.781255564438686</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>4.760211259164442</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>4.739377396942941</v>
+        <v>0</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>4.718751873343655</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4.698332604980362</v>
+        <v>0</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>3.654559875003377</v>
+        <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>2.617953880133723</v>
+        <v>0</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>2.607349780229534</v>
+        <v>0</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>2.596851721324386</v>
+        <v>0</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>2.586458643008291</v>
+        <v>0</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>2.527899077620143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1688,155 +1577,107 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0</v>
+        <v>25.44686120688618</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>36.36577111173804</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0</v>
+        <v>51.37173908907033</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>0</v>
+        <v>66.31775510398687</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>81.20472209168821</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>96.03353092386709</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>110.8050605596852</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0</v>
+        <v>115.4446554697099</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>0</v>
+        <v>118.0951584733858</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>0</v>
+        <v>120.7376308653372</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>0</v>
+        <v>123.3722042626448</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>0</v>
+        <v>125.9990084531091</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>D&amp;A</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>25.44686120688618</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>36.36577111173804</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>51.37173908907033</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>66.31775510398687</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>81.20472209168821</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>96.03353092386709</v>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>110.8050605596852</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>115.4446554697099</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>118.0951584733858</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>120.7376308653372</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>123.3722042626448</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>125.9990084531091</v>
-      </c>
-    </row>
-    <row r="8" ht="15.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C7" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2890" yWindow="1010" windowWidth="8060" windowHeight="7730" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Electricity" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LPG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LPG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Electricity &amp; E-Cooking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Electricity (Low access)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
@@ -529,768 +530,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr codeName="Hoja2">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="15.1796875" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="9.08984375" bestFit="1" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.5" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>Type - Inputs</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Inputs</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="n">
-        <v>2023</v>
-      </c>
-      <c r="E1" s="4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F1" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H1" s="4" t="n">
-        <v>2027</v>
-      </c>
-      <c r="I1" s="4" t="n">
-        <v>2028</v>
-      </c>
-      <c r="J1" s="4" t="n">
-        <v>2029</v>
-      </c>
-      <c r="K1" s="4" t="n">
-        <v>2030</v>
-      </c>
-      <c r="L1" s="4" t="n">
-        <v>2031</v>
-      </c>
-      <c r="M1" s="4" t="n">
-        <v>2032</v>
-      </c>
-      <c r="N1" s="4" t="n">
-        <v>2033</v>
-      </c>
-      <c r="O1" s="4" t="n">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="2" ht="15.5" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>1473.5735</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>1616.8539</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>1793.1866</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>1954.5022</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>2101.5716</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>2235.1395</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>2355.9236</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>2518.5404</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>2659.5132</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>2786.3986</v>
-      </c>
-      <c r="N2" s="8" t="n">
-        <v>3222.2</v>
-      </c>
-      <c r="O2" s="8" t="n">
-        <v>3001.0062</v>
-      </c>
-    </row>
-    <row r="3" ht="15.5" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15.5" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Growth</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>257.2547513691348</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>324.6150491019822</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>321.3688986109623</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>318.1552096248527</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>314.9736575286042</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>311.8239209533182</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>382.0048802582858</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>451.1166131276156</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>446.6054469963394</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>442.139392526376</v>
-      </c>
-      <c r="N4" s="8" t="n">
-        <v>437.7179986011122</v>
-      </c>
-      <c r="O4" s="8" t="n">
-        <v>290.7814303112916</v>
-      </c>
-    </row>
-    <row r="5" ht="15.5" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="15.5" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>48.20089562467992</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>54.57954899290949</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>62.19293437018627</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>69.64859408501823</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>76.94892131211654</v>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>84.09627713526439</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>91.09299094981805</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>102.1514263745141</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>112.6977094229257</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>123.0228516677316</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>133.1302212966991</v>
-      </c>
-      <c r="O6" s="8" t="n">
-        <v>143.0231412479205</v>
-      </c>
-    </row>
-    <row r="7" ht="15.5" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>GRID</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15.5" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>368.3935</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>379.2621</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>393.6264</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>400.3198</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>400.2994</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>394.4365</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>383.5224</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>376.3336</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>362.6608</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>344.3864</v>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>322.22</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="n">
-        <v>296.8028</v>
-      </c>
-    </row>
-    <row r="9" ht="15.5" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15.5" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Growth</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>39.54004604566455</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>50.33243931157392</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>49.82911491845817</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>49.3308237692736</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>48.83751553158086</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>48.34914037626506</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>15.38261584720839</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>-17.09142019004943</v>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>-16.92050598814893</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>-16.75130092826744</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>-16.58378791898477</v>
-      </c>
-      <c r="O10" s="8" t="n">
-        <v>-1.667201492973772</v>
-      </c>
-    </row>
-    <row r="11" ht="15.5" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CAPEX - Maintenance</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>M$</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>56.13416700255231</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>64.73926242752357</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>74.87567895765055</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>84.80289323093224</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>94.52407565085252</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>104.0423541330513</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>113.360814638041</v>
-      </c>
-      <c r="K12" s="8" t="n">
-        <v>111.5849676293287</v>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>105.1265326494934</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>98.78610787249185</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>92.56197893776543</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>86.45245397094627</v>
-      </c>
-    </row>
-    <row r="13" ht="15.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>OFF-GRID</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15.5" customHeight="1">
-      <c r="D16" s="16" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1686,4 +925,1608 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15.1796875" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="9.08984375" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Type - Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I1" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J1" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K1" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L1" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="M1" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N1" s="4" t="n">
+        <v>2033</v>
+      </c>
+      <c r="O1" s="4" t="n">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>1473.57</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>1616.85</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>1793.19</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>1954.5</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>2101.57</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>2235.14</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>2355.92</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>2518.54</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>2659.51</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>2786.4</v>
+      </c>
+      <c r="N2" s="8" t="n">
+        <v>3222.2</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>3001.01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>321.37</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>318.16</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>314.97</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>382</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>451.12</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>446.61</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>442.14</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>437.7179986011</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>290.78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Maintenance</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>133.1302212967</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>143.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>368.39</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>393.63</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>400.32</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>400.3</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>394.44</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>383.52</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>376.33</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>362.66</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>322.22</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>296.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>-17.09</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>-16.92</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>-16.75</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>-16.583787919</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Maintenance</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>104.04</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>111.58</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>92.56197893780001</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>86.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15.1796875" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="9.08984375" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Type - Inputs</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="I1" s="4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J1" s="4" t="n">
+        <v>2029</v>
+      </c>
+      <c r="K1" s="4" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L1" s="4" t="n">
+        <v>2031</v>
+      </c>
+      <c r="M1" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N1" s="4" t="n">
+        <v>2033</v>
+      </c>
+      <c r="O1" s="4" t="n">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O2" s="10" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>321.37</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>318.16</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>314.97</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>311.82</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>382</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>451.12</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>446.61</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>442.14</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>437.7179986011</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>290.78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Maintenance</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>76.95</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>133.1302212967</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>143.02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GRID</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>118.39</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>129.26</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>143.63</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>150.32</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>144.44</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>133.52</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>126.33</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>112.66</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>94.39</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>322.22</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Outputs</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Growth</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>-17.09</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>-16.92</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>-16.75</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>-16.583787919</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CAPEX - Maintenance</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>M$</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>104.04</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>113.36</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>111.58</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>98.79000000000001</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>92.56197893780001</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>86.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>OFF-GRID</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2890" yWindow="1010" windowWidth="8060" windowHeight="7730" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="LPG" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,9 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -137,7 +135,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -178,22 +176,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -535,12 +522,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col width="20.81640625" customWidth="1" min="1" max="1"/>
+    <col width="20.77734375" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.5" customHeight="1">
+    <row r="1" ht="15.45" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Inputs</t>
@@ -588,7 +575,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="2" ht="15.5" customHeight="1">
+    <row r="2" ht="15.45" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Demand</t>
@@ -599,44 +586,44 @@
           <t>kWh</t>
         </is>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="8" t="n">
         <v>301.937024</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="8" t="n">
         <v>326.61092</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="8" t="n">
         <v>438.647661</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="8" t="n">
         <v>539.273622</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="8" t="n">
         <v>629.321493</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="8" t="n">
         <v>709.570533</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="8" t="n">
         <v>780.749774</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="J2" s="8" t="n">
         <v>970.466594</v>
       </c>
-      <c r="K2" s="14" t="n">
+      <c r="K2" s="8" t="n">
         <v>949.431507</v>
       </c>
-      <c r="L2" s="14" t="n">
+      <c r="L2" s="8" t="n">
         <v>928.199157</v>
       </c>
-      <c r="M2" s="14" t="n">
+      <c r="M2" s="8" t="n">
         <v>906.8360300000001</v>
       </c>
-      <c r="N2" s="14" t="n">
+      <c r="N2" s="8" t="n">
         <v>885.402727</v>
       </c>
     </row>
-    <row r="3" ht="15.5" customHeight="1">
+    <row r="3" ht="15.45" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Outputs</t>
@@ -708,7 +695,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.5" customHeight="1">
+    <row r="4" ht="15.45" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CAPEX - Growth</t>
@@ -756,7 +743,7 @@
         <v>2.527899077620143</v>
       </c>
     </row>
-    <row r="5" ht="15.5" customHeight="1">
+    <row r="5" ht="15.45" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CAPEX - Maintenance</t>
@@ -804,7 +791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15.5" customHeight="1">
+    <row r="6" ht="15.45" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -852,7 +839,7 @@
         <v>125.9990084531091</v>
       </c>
     </row>
-    <row r="7" ht="15.5" customHeight="1">
+    <row r="7" ht="15.45" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>D&amp;A</t>
@@ -934,14 +921,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.1796875" customWidth="1" min="1" max="1"/>
+    <col width="15.21875" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="9.08984375" customWidth="1" min="4" max="4"/>
+    <col width="9.109375" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.6" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Type - Inputs</t>
@@ -994,7 +981,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1041,13 +1028,13 @@
         <v>2786.4</v>
       </c>
       <c r="N2" s="8" t="n">
-        <v>3222.2</v>
+        <v>2899.98</v>
       </c>
       <c r="O2" s="8" t="n">
         <v>3001.01</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.6" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1124,7 +1111,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.6" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1141,43 +1128,43 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>257.2547513691348</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>324.62</v>
+        <v>324.6150491019822</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>321.37</v>
+        <v>321.3688986109623</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>318.16</v>
+        <v>318.1552096248527</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>314.97</v>
+        <v>314.9736575286042</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>311.82</v>
+        <v>311.8239209533182</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>382</v>
+        <v>382.0048802582858</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>451.12</v>
+        <v>451.1166131276156</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>446.61</v>
+        <v>446.6054469963394</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>442.14</v>
+        <v>442.139392526376</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>437.7179986011</v>
+        <v>437.7179986011122</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>290.78</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>290.7814303112916</v>
+      </c>
+    </row>
+    <row r="5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1230,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1247,10 +1234,10 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1</v>
+        <v>48.20089562467992</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2</v>
+        <v>54.57954899290949</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>62.19</v>
@@ -1283,7 +1270,7 @@
         <v>143.02</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1358,7 +1345,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.6" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1404,16 +1391,14 @@
       <c r="M8" s="10" t="n">
         <v>344.39</v>
       </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>322.22</t>
-        </is>
+      <c r="N8" s="10" t="n">
+        <v>322.22</v>
       </c>
       <c r="O8" s="10" t="n">
         <v>296.8</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.6" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> OFF-GRID</t>
@@ -1490,7 +1475,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.6" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1543,7 +1528,7 @@
         <v>-1.67</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.6" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1596,7 +1581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.6" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1613,10 +1598,10 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1</v>
+        <v>56.13416700255231</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2</v>
+        <v>64.73926242752357</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>74.88</v>
@@ -1649,7 +1634,7 @@
         <v>86.45</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.6" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -1735,15 +1720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="15.1796875" customWidth="1" min="1" max="1"/>
+    <col width="15.21875" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="9.08984375" customWidth="1" min="4" max="4"/>
+    <col width="9.109375" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.6" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Type - Inputs</t>
@@ -1796,7 +1781,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1813,43 +1798,43 @@
         </is>
       </c>
       <c r="D2" s="10" t="n">
-        <v>1000</v>
+        <v>1442.594335096599</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1000</v>
+        <v>1496.414222138419</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>1000</v>
+        <v>1584.425336361194</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>1000</v>
+        <v>1666.112638748381</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>1000</v>
+        <v>1741.607668943678</v>
       </c>
       <c r="I2" s="10" t="n">
-        <v>1000</v>
+        <v>1811.068812728656</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1000</v>
+        <v>1874.67577123492</v>
       </c>
       <c r="K2" s="10" t="n">
-        <v>1000</v>
+        <v>1933.650156760106</v>
       </c>
       <c r="L2" s="10" t="n">
-        <v>1000</v>
+        <v>1991.305039979616</v>
       </c>
       <c r="M2" s="10" t="n">
-        <v>1000</v>
+        <v>2044.132836459943</v>
       </c>
       <c r="N2" s="10" t="n">
-        <v>1000</v>
+        <v>2092.231625021555</v>
       </c>
       <c r="O2" s="10" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>2135.694853592131</v>
+      </c>
+    </row>
+    <row r="3" ht="15.6" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1926,7 +1911,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.6" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -1943,43 +1928,43 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>214.8267851046716</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>2</v>
+        <v>248.0600347279134</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>321.37</v>
+        <v>245.5794343806341</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>318.16</v>
+        <v>243.1236400368279</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>314.97</v>
+        <v>240.6924036364595</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>311.82</v>
+        <v>238.285479600095</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>382</v>
+        <v>276.1328264022534</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>451.12</v>
+        <v>313.4000433206662</v>
       </c>
       <c r="L4" s="8" t="n">
-        <v>446.61</v>
+        <v>310.2660428874595</v>
       </c>
       <c r="M4" s="8" t="n">
-        <v>442.14</v>
+        <v>307.1633824585849</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>437.7179986011</v>
+        <v>304.091748633999</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>290.78</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>208.5872747268976</v>
+      </c>
+    </row>
+    <row r="5" ht="15.6" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -2032,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.6" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -2049,43 +2034,43 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>3</v>
+        <v>46.18373564251058</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>3</v>
+        <v>47.90691898003998</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>62.19</v>
+        <v>50.88846742688325</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>69.65000000000001</v>
+        <v>53.81281018084225</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>76.95</v>
+        <v>56.66899623297937</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>84.09999999999999</v>
+        <v>59.46564228305566</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>91.09</v>
+        <v>62.19138351250714</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>102.15</v>
+        <v>70.98921284704677</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>112.7</v>
+        <v>81.31186812507968</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>123.02</v>
+        <v>91.41218637626721</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>133.1302212967</v>
+        <v>101.3102583723185</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>143.02</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>110.9952915423451</v>
+      </c>
+    </row>
+    <row r="7" ht="15.6" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GRID</t>
@@ -2160,7 +2145,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.6" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -2177,45 +2162,43 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>118.39</v>
+        <v>368.39</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>129.26</v>
+        <v>379.26</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>143.63</v>
+        <v>393.63</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>150.32</v>
+        <v>400.32</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>150.3</v>
+        <v>400.3</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>144.44</v>
+        <v>394.44</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>133.52</v>
+        <v>383.52</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>126.33</v>
+        <v>376.33</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>112.66</v>
+        <v>362.66</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>94.39</v>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>322.22</t>
-        </is>
+        <v>344.39</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>322.22</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>46.8</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>296.8</v>
+      </c>
+    </row>
+    <row r="9" ht="15.6" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve"> OFF-GRID</t>
@@ -2292,7 +2275,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15.6" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -2345,7 +2328,7 @@
         <v>-1.67</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15.6" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -2398,7 +2381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.6" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -2415,10 +2398,10 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>56.13416700255231</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2</v>
+        <v>64.73926242752357</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>74.88</v>
@@ -2451,7 +2434,7 @@
         <v>86.45</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.6" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>OFF-GRID</t>
@@ -2525,6 +2508,20 @@
           <t>-</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="14" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-CleanStep.xlsx
@@ -129,7 +129,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -162,6 +162,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
